--- a/batches/2026-09-17_1737ET_fix_other_names_former/lng_carrier_fix.xlsx
+++ b/batches/2026-09-17_1737ET_fix_other_names_former/lng_carrier_fix.xlsx
@@ -511,7 +511,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Rows corrected: 160   Refs checked: 237   Refs dropped/removed: 0</t>
+          <t>Rows corrected: 160   Refs checked: 239   Refs dropped/removed: 0</t>
         </is>
       </c>
     </row>
@@ -20292,14 +20292,14 @@
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>Karmol LNGT Powership Antarctica; Northwest Sanderling</t>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>Karmol LNGT Powership Antarctica; Karadeniz LNGT Antarctica; Northwest Sanderling</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.lngindustry.com/regasification/28052025/karpowership-celebrates-fsru-undocking-with-karmol-and-seatrium/, https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -29512,7 +29512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F238"/>
+  <dimension ref="A1:F240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -35456,29 +35456,29 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Karmol LNGT Powership Antarctica; Northwest Sanderling</t>
+          <t>Karmol LNGT Powership Antarctica; Karadeniz LNGT Antarctica; Northwest Sanderling</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.lngindustry.com/regasification/28052025/karpowership-celebrates-fsru-undocking-with-karmol-and-seatrium/</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Karmol LNGT Powership Antarctica'; the row is renamed 'Karadeniz LNGT Antarctica' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Antarctica (ex-Northwest Sanderling)'</t>
+          <t>former Name 'Karmol LNGT Powership Antarctica' (lngindustry.com, 2025-05-28); the row is renamed 'LNGT Antarctica' by 2026-09-17_1654ET_fix_igu2026_sourced; IGU 2026 prints 'Karadeniz LNGT Antarctica (ex-Northwest Sanderling)' — both IGU names carried here (Baird 2026-09-18)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -35488,7 +35488,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>LNGT Americas; Northwest Stormpetrel</t>
+          <t>Karmol LNGT Powership Antarctica; Karadeniz LNGT Antarctica; Northwest Sanderling</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -35503,14 +35503,14 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>former Name 'LNGT Americas'; the row is renamed 'Karadeniz LNGT Americas' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Americas (ex-Northwest Stormpetrel)'</t>
+          <t>former Name 'Karmol LNGT Powership Antarctica' (lngindustry.com, 2025-05-28); the row is renamed 'LNGT Antarctica' by 2026-09-17_1654ET_fix_igu2026_sourced; IGU 2026 prints 'Karadeniz LNGT Antarctica (ex-Northwest Sanderling)' — both IGU names carried here (Baird 2026-09-18)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -35520,7 +35520,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Puteri Intan</t>
+          <t>Karmol LNGT Powership Antarctica; Karadeniz LNGT Antarctica; Northwest Sanderling</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -35530,19 +35530,19 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Puteri Intan'; the row is renamed 'American Energy' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Karmol LNGT Powership Antarctica' (lngindustry.com, 2025-05-28); the row is renamed 'LNGT Antarctica' by 2026-09-17_1654ET_fix_igu2026_sourced; IGU 2026 prints 'Karadeniz LNGT Antarctica (ex-Northwest Sanderling)' — both IGU names carried here (Baird 2026-09-18)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>811</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -35552,7 +35552,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>KLNGTP Black Sea; Portovenere; LNG Portovenere</t>
+          <t>LNGT Americas; Northwest Stormpetrel</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -35562,19 +35562,19 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>former Name 'KLNGTP Black Sea'; the row is renamed 'Karadeniz LNGT Powership Black Sea' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'</t>
+          <t>former Name 'LNGT Americas'; the row is renamed 'Karadeniz LNGT Americas' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Americas (ex-Northwest Stormpetrel)'</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>971</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -35584,7 +35584,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>KLNGTP Black Sea; Portovenere; LNG Portovenere</t>
+          <t>Puteri Intan</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -35594,19 +35594,19 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>former Name 'KLNGTP Black Sea'; the row is renamed 'Karadeniz LNGT Powership Black Sea' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'</t>
+          <t>former Name 'Puteri Intan'; the row is renamed 'American Energy' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>726</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -35616,7 +35616,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>KLNGTP Marmara; Lerici; LNG Lerici</t>
+          <t>KLNGTP Black Sea; Portovenere; LNG Portovenere</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -35631,14 +35631,14 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>former Name 'KLNGTP Marmara'; the row is renamed 'Karadeniz LNGT Powership Marmara' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'</t>
+          <t>former Name 'KLNGTP Black Sea'; the row is renamed 'Karadeniz LNGT Powership Black Sea' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>726</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -35648,7 +35648,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>KLNGTP Marmara; Lerici; LNG Lerici</t>
+          <t>KLNGTP Black Sea; Portovenere; LNG Portovenere</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -35658,19 +35658,19 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>former Name 'KLNGTP Marmara'; the row is renamed 'Karadeniz LNGT Powership Marmara' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'</t>
+          <t>former Name 'KLNGTP Black Sea'; the row is renamed 'Karadeniz LNGT Powership Black Sea' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>727</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -35680,29 +35680,29 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Seapeak Hispania</t>
+          <t>KLNGTP Marmara; Lerici; LNG Lerici</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/115017</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Seapeak Hispania'; the row is renamed 'Seapeak Jupiter' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'KLNGTP Marmara'; the row is renamed 'Karadeniz LNGT Powership Marmara' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>727</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -35712,29 +35712,29 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Seapeak Hispania</t>
+          <t>KLNGTP Marmara; Lerici; LNG Lerici</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/115017</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Seapeak Hispania'; the row is renamed 'Seapeak Jupiter' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'KLNGTP Marmara'; the row is renamed 'Karadeniz LNGT Powership Marmara' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -35744,12 +35744,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Energy Frontier</t>
+          <t>Seapeak Hispania</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/116125</t>
+          <t>https://www.shipvault.com/ships/115017</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -35759,14 +35759,14 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Energy Frontier'; the row is renamed 'Arunika Jaya' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Seapeak Hispania'; the row is renamed 'Seapeak Jupiter' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -35776,12 +35776,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Energy Frontier</t>
+          <t>Seapeak Hispania</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116125</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/115017</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -35791,14 +35791,14 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Energy Frontier'; the row is renamed 'Arunika Jaya' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Seapeak Hispania'; the row is renamed 'Seapeak Jupiter' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>562</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -35808,12 +35808,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Golar Arctic</t>
+          <t>Energy Frontier</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/116640</t>
+          <t>https://www.shipvault.com/ships/116125</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -35823,14 +35823,14 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Golar Arctic'; the row is renamed 'SC Serenity' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Energy Frontier'; the row is renamed 'Arunika Jaya' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>562</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -35840,12 +35840,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Golar Arctic</t>
+          <t>Energy Frontier</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116640</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116125</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -35855,14 +35855,14 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Golar Arctic'; the row is renamed 'SC Serenity' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Energy Frontier'; the row is renamed 'Arunika Jaya' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>648</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -35872,29 +35872,29 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Metagas Everest</t>
+          <t>Golar Arctic</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.shipvault.com/ships/116640</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Metagas Everest'; the row is renamed 'Arctic Metagas' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Golar Arctic'; the row is renamed 'SC Serenity' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>648</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -35904,29 +35904,29 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>LNG River Orashi</t>
+          <t>Golar Arctic</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116640</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>former Name 'LNG River Orashi'; the row is renamed 'Gas Garuda' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Golar Arctic'; the row is renamed 'SC Serenity' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>866</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -35936,7 +35936,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>LNG Pioneer; Pioneer Spirit</t>
+          <t>Metagas Everest</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -35951,14 +35951,14 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Pioneer Spirit'; the row is renamed 'Arctic Pioneer' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Metagas Everest'; the row is renamed 'Arctic Metagas' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>801</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -35968,7 +35968,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Condor LNG; CCH LNG; Methane Lydon Volney</t>
+          <t>LNG River Orashi</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -35983,14 +35983,14 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>former Name 'CCH LNG'; the row is renamed 'LNG Soars' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'LNG Soars (ex-Methane Lydon Volney)'</t>
+          <t>former Name 'LNG River Orashi'; the row is renamed 'Gas Garuda' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>958</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -36000,7 +36000,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Methane Heather Sally</t>
+          <t>LNG Pioneer; Pioneer Spirit</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -36010,19 +36010,19 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Methane Heather Sally'; the row is renamed 'Shandong Redwood' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Pioneer Spirit'; the row is renamed 'Arctic Pioneer' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -36032,7 +36032,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Golar Tundra</t>
+          <t>Condor LNG; CCH LNG; Methane Lydon Volney</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -36047,14 +36047,14 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Golar Tundra'; the row is renamed 'Italis LNG' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'CCH LNG'; the row is renamed 'LNG Soars' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'LNG Soars (ex-Methane Lydon Volney)'</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>869</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -36064,29 +36064,29 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Kool Baltic; SCF Melampus</t>
+          <t>Methane Heather Sally</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/3928</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Kool Baltic'; the row is renamed 'Cool Baltic' by 2026-09-17_1654ET_fix_igu2026_sourced; plus IGU 2026 prints 'Cool Baltic (ex-SCF Melampus)'</t>
+          <t>former Name 'Methane Heather Sally'; the row is renamed 'Shandong Redwood' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>649</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -36096,22 +36096,22 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Kool Baltic; SCF Melampus</t>
+          <t>Golar Tundra</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/3928</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Kool Baltic'; the row is renamed 'Cool Baltic' by 2026-09-17_1654ET_fix_igu2026_sourced; plus IGU 2026 prints 'Cool Baltic (ex-SCF Melampus)'</t>
+          <t>former Name 'Golar Tundra'; the row is renamed 'Italis LNG' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
@@ -36133,12 +36133,12 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.shipvault.com/ships/3928</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
@@ -36150,7 +36150,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>729</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -36160,29 +36160,29 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>SCF La Perouse</t>
+          <t>Kool Baltic; SCF Melampus</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/3928</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>former Name 'SCF La Perouse'; the row is renamed 'La Perouse' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Kool Baltic'; the row is renamed 'Cool Baltic' by 2026-09-17_1654ET_fix_igu2026_sourced; plus IGU 2026 prints 'Cool Baltic (ex-SCF Melampus)'</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>729</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -36192,7 +36192,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Hull 3342 (HDHHI)</t>
+          <t>Kool Baltic; SCF Melampus</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -36207,14 +36207,14 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Apostolos (ex-Hyundai 3342)' — hull-number former name written as the QC §2 placeholder 'Hull 3342 (HDHHI)'</t>
+          <t>former Name 'Kool Baltic'; the row is renamed 'Cool Baltic' by 2026-09-17_1654ET_fix_igu2026_sourced; plus IGU 2026 prints 'Cool Baltic (ex-SCF Melampus)'</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>993</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -36224,7 +36224,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Hull 3341 (HDHHI)</t>
+          <t>SCF La Perouse</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -36239,14 +36239,14 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Assos (ex-3341)' — hull-number former name written as the QC §2 placeholder 'Hull 3341 (HDHHI)'</t>
+          <t>former Name 'SCF La Perouse'; the row is renamed 'La Perouse' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>385</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -36256,7 +36256,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Hull 2635 (SHI)</t>
+          <t>Hull 3342 (HDHHI)</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -36271,14 +36271,14 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Athos LNG (ex-Samsung 2635)' — hull-number former name written as the QC §2 placeholder 'Hull 2635 (SHI)'</t>
+          <t>IGU 2026 prints 'Apostolos (ex-Hyundai 3342)' — hull-number former name written as the QC §2 placeholder 'Hull 3342 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -36288,7 +36288,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Hull 2584 (SHI)</t>
+          <t>Hull 3341 (HDHHI)</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -36303,14 +36303,14 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Celsius Greenwich (ex-2584)' — hull-number former name written as the QC §2 placeholder 'Hull 2584 (SHI)'</t>
+          <t>IGU 2026 prints 'Assos (ex-3341)' — hull-number former name written as the QC §2 placeholder 'Hull 3341 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -36320,7 +36320,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Hull 3293 (HDHHI)</t>
+          <t>Hull 2635 (SHI)</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -36335,14 +36335,14 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Clean Future (ex-3293)' — hull-number former name written as the QC §2 placeholder 'Hull 3293 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Athos LNG (ex-Samsung 2635)' — hull-number former name written as the QC §2 placeholder 'Hull 2635 (SHI)'</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -36352,7 +36352,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Hull 1881A (Hudong)</t>
+          <t>Hull 2584 (SHI)</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -36362,19 +36362,19 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Greenergy Pearl (ex-Hudong-Zhonghua H1881A)' — hull-number former name written as the QC §2 placeholder 'Hull 1881A (Hudong)'</t>
+          <t>IGU 2026 prints 'Celsius Greenwich (ex-2584)' — hull-number former name written as the QC §2 placeholder 'Hull 2584 (SHI)'</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -36384,7 +36384,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Hull 1792A (Hudong)</t>
+          <t>Hull 3293 (HDHHI)</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -36399,14 +36399,14 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Hlaitan (ex-H1792A)' — hull-number former name written as the QC §2 placeholder 'Hull 1792A (Hudong)'</t>
+          <t>IGU 2026 prints 'Clean Future (ex-3293)' — hull-number former name written as the QC §2 placeholder 'Hull 3293 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -36416,7 +36416,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>LNG Unity; Provalys</t>
+          <t>Hull 1881A (Hudong)</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -36431,14 +36431,14 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Karadeniz LNGT Powership Anatolia (ex-LNG Unity / ex-Provalys)'; Provalys</t>
+          <t>IGU 2026 prints 'Greenergy Pearl (ex-Hudong-Zhonghua H1881A)' — hull-number former name written as the QC §2 placeholder 'Hull 1881A (Hudong)'</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -36448,7 +36448,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>LNG Unity; Provalys</t>
+          <t>Hull 1792A (Hudong)</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -36463,14 +36463,14 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Karadeniz LNGT Powership Anatolia (ex-LNG Unity / ex-Provalys)'; Provalys</t>
+          <t>IGU 2026 prints 'Hlaitan (ex-H1792A)' — hull-number former name written as the QC §2 placeholder 'Hull 1792A (Hudong)'</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>719</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -36480,7 +36480,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Dwiputra</t>
+          <t>LNG Unity; Provalys</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -36490,19 +36490,19 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Karmol LNGT Powership Africa (ex-Dwiputra)'</t>
+          <t>IGU 2026 prints 'Karadeniz LNGT Powership Anatolia (ex-LNG Unity / ex-Provalys)'; Provalys</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>719</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -36512,7 +36512,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Northwest Shearwater</t>
+          <t>LNG Unity; Provalys</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -36522,19 +36522,19 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Karmol LNGT Powership Asia (ex-Northwest Shearwater)'</t>
+          <t>IGU 2026 prints 'Karadeniz LNGT Powership Anatolia (ex-LNG Unity / ex-Provalys)'; Provalys</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>720</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -36544,7 +36544,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Hull 1836A (Hudong)</t>
+          <t>Dwiputra</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -36554,19 +36554,19 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Kongtong (ex-Hudong-Zhonghua H1836A)' — hull-number former name written as the QC §2 placeholder 'Hull 1836A (Hudong)'</t>
+          <t>IGU 2026 prints 'Karmol LNGT Powership Africa (ex-Dwiputra)'</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -36576,7 +36576,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>SCF Mitre</t>
+          <t>Northwest Shearwater</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -36586,19 +36586,19 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Kool Boreas (ex-SCF Mitre)'</t>
+          <t>IGU 2026 prints 'Karmol LNGT Powership Asia (ex-Northwest Shearwater)'</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>SCF Barents</t>
+          <t>Hull 1836A (Hudong)</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -36623,14 +36623,14 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Kool Firn (ex-SCF Barents)'</t>
+          <t>IGU 2026 prints 'Kongtong (ex-Hudong-Zhonghua H1836A)' — hull-number former name written as the QC §2 placeholder 'Hull 1836A (Hudong)'</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>731</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -36640,7 +36640,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Hull 3221 (HDHHI)</t>
+          <t>SCF Mitre</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -36655,14 +36655,14 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'New Brave (ex-3221)' — hull-number former name written as the QC §2 placeholder 'Hull 3221 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Kool Boreas (ex-SCF Mitre)'</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -36672,7 +36672,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Hull 3224 (HDHHI)</t>
+          <t>SCF Barents</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -36682,19 +36682,19 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'New Green ST (ex-3224)' — hull-number former name written as the QC §2 placeholder 'Hull 3224 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Kool Firn (ex-SCF Barents)'</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -36704,7 +36704,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Hull 3222 (HDHHI)</t>
+          <t>Hull 3221 (HDHHI)</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -36719,14 +36719,14 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'New Nature (ex-3222)' — hull-number former name written as the QC §2 placeholder 'Hull 3222 (HDHHI)'</t>
+          <t>IGU 2026 prints 'New Brave (ex-3221)' — hull-number former name written as the QC §2 placeholder 'Hull 3221 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>172</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -36736,7 +36736,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Hull 2592 (SHI)</t>
+          <t>Hull 3224 (HDHHI)</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -36751,14 +36751,14 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Orion Spirit (ex-2592)' — hull-number former name written as the QC §2 placeholder 'Hull 2592 (SHI)'</t>
+          <t>IGU 2026 prints 'New Green ST (ex-3224)' — hull-number former name written as the QC §2 placeholder 'Hull 3224 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -36768,7 +36768,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Hull 2315 (SHI)</t>
+          <t>Hull 3222 (HDHHI)</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -36778,19 +36778,19 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Pacific Success (ex-Samsung Heavy Industries 2315)' — hull-number former name written as the QC §2 placeholder 'Hull 2315 (SHI)'</t>
+          <t>IGU 2026 prints 'New Nature (ex-3222)' — hull-number former name written as the QC §2 placeholder 'Hull 3222 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -36800,7 +36800,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Hull 3297 (HDHHI)</t>
+          <t>Hull 2592 (SHI)</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -36815,14 +36815,14 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Puteri Ledang (ex-Hull 3297)' — hull-number former name written as the QC §2 placeholder 'Hull 3297 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Orion Spirit (ex-2592)' — hull-number former name written as the QC §2 placeholder 'Hull 2592 (SHI)'</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -36832,7 +36832,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Hull 3298 (HDHHI)</t>
+          <t>Hull 2315 (SHI)</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -36842,19 +36842,19 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Puteri Mahsuri (ex-Hull 3298)' — hull-number former name written as the QC §2 placeholder 'Hull 3298 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Pacific Success (ex-Samsung Heavy Industries 2315)' — hull-number former name written as the QC §2 placeholder 'Hull 2315 (SHI)'</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>176</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -36864,7 +36864,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Hull 3295 (HDHHI)</t>
+          <t>Hull 3297 (HDHHI)</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -36879,14 +36879,14 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Puteri Santubong (ex-Hull 3295)' — hull-number former name written as the QC §2 placeholder 'Hull 3295 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Puteri Ledang (ex-Hull 3297)' — hull-number former name written as the QC §2 placeholder 'Hull 3297 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -36896,7 +36896,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Hull 3299 (HSHI)</t>
+          <t>Hull 3298 (HDHHI)</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -36911,14 +36911,14 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Puteri Mayang (ex-Hull 3299)' — hull-number former name written as the QC §2 placeholder 'Hull 3299 (HSHI)'</t>
+          <t>IGU 2026 prints 'Puteri Mahsuri (ex-Hull 3298)' — hull-number former name written as the QC §2 placeholder 'Hull 3298 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -36928,7 +36928,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Hull H1793A (Hudong)</t>
+          <t>Hull 3295 (HDHHI)</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -36938,19 +36938,19 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Limail (ex-Hudong Hull 1793A)' — hull-number former name written as the QC §2 placeholder 'Hull H1793A (Hudong)'</t>
+          <t>IGU 2026 prints 'Puteri Santubong (ex-Hull 3295)' — hull-number former name written as the QC §2 placeholder 'Hull 3295 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>972</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -36960,7 +36960,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Hull 2527 (Hanwha)</t>
+          <t>Hull 3299 (HSHI)</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -36975,14 +36975,14 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'MOL Azure (ex-Hull 2527)' — hull-number former name written as the QC §2 placeholder 'Hull 2527 (Hanwha)'</t>
+          <t>IGU 2026 prints 'Puteri Mayang (ex-Hull 3299)' — hull-number former name written as the QC §2 placeholder 'Hull 3299 (HSHI)'</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>257</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -36992,7 +36992,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Hull 3225 (HDHHI)</t>
+          <t>Hull H1793A (Hudong)</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -37002,19 +37002,19 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'New Oasis (ex-Hyundai 3225)' — hull-number former name written as the QC §2 placeholder 'Hull 3225 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Limail (ex-Hudong Hull 1793A)' — hull-number former name written as the QC §2 placeholder 'Hull H1793A (Hudong)'</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>885</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -37024,7 +37024,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Hull 2566 (Hanwha)</t>
+          <t>Hull 2527 (Hanwha)</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -37039,14 +37039,14 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Esteem Fuji (ex-Hull 2566)' — hull-number former name written as the QC §2 placeholder 'Hull 2566 (Hanwha)'</t>
+          <t>IGU 2026 prints 'MOL Azure (ex-Hull 2527)' — hull-number former name written as the QC §2 placeholder 'Hull 2527 (Hanwha)'</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>915</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -37056,7 +37056,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Hull 2537 (Hanwha)</t>
+          <t>Hull 3225 (HDHHI)</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -37071,14 +37071,14 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Maran Gas Syros (ex-ABCDE (2537))' — hull-number former name written as the QC §2 placeholder 'Hull 2537 (Hanwha)'</t>
+          <t>IGU 2026 prints 'New Oasis (ex-Hyundai 3225)' — hull-number former name written as the QC §2 placeholder 'Hull 3225 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Hull H1892A (Hudong)</t>
+          <t>Hull 2566 (Hanwha)</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -37098,42 +37098,106 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Ocean Inspiration (ex-Hudong-Zhonghua H1892A)' — hull-number former name written as the QC §2 placeholder 'Hull H1892A (Hudong)'</t>
+          <t>IGU 2026 prints 'Esteem Fuji (ex-Hull 2566)' — hull-number former name written as the QC §2 placeholder 'Hull 2566 (Hanwha)'</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Hull 2537 (Hanwha)</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'Maran Gas Syros (ex-ABCDE (2537))' — hull-number former name written as the QC §2 placeholder 'Hull 2537 (Hanwha)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Hull H1892A (Hudong)</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (all tokens present))</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'Ocean Inspiration (ex-Hudong-Zhonghua H1892A)' — hull-number former name written as the QC §2 placeholder 'Hull H1892A (Hudong)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
           <t>1111</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>Other names</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>Hull 2535 (Hanwha)</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>PASS (corroborates)</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>IGU 2026 prints 'Woodside Barrumbara (ex-2535)' — hull-number former name written as the QC §2 placeholder 'Hull 2535 (Hanwha)'</t>
         </is>

--- a/batches/2026-09-17_1737ET_fix_other_names_former/lng_carrier_fix.xlsx
+++ b/batches/2026-09-17_1737ET_fix_other_names_former/lng_carrier_fix.xlsx
@@ -511,7 +511,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Rows corrected: 160   Refs checked: 239   Refs dropped/removed: 0</t>
+          <t>Rows corrected: 162   Refs checked: 252   Refs dropped/removed: 0</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT161"/>
+  <dimension ref="A1:AT163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/458163</t>
+          <t>https://www.shipvault.com/ships/458163, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/458163</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -20466,7 +20466,7 @@
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>LNGT Americas; Northwest Stormpetrel</t>
+          <t>LNGT Americas; Karadeniz LNGT Americas; Northwest Stormpetrel</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
@@ -20832,14 +20832,14 @@
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>KLNGTP Black Sea; Portovenere; LNG Portovenere</t>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>Karadeniz LNGT Powership Black Sea; Portovenere; LNG Portovenere</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf, https://www.marinetraffic.org/ship-owner-manager-ism-data/KARADENIZ-LNGT-POWERSHIP-BLACK-SEA/9064073/352004132</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
@@ -21016,14 +21016,14 @@
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>KLNGTP Marmara; Lerici; LNG Lerici</t>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>Karadeniz LNGT Powership Marmara; Lerici; LNG Lerici</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf, https://www.marinetraffic.org/ship-owner-manager-ism-data/KARADENIZ-LNGT-POWERSHIP-MARMARA/9064085/352004078</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -21380,14 +21380,14 @@
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>Seapeak Hispania</t>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Seapeak Hispania; Seapeak Jupiter</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/115017, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/115017</t>
+          <t>https://www.shipvault.com/ships/115017, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/115017, https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -21934,7 +21934,7 @@
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>Metagas Everest</t>
+          <t>Metagas Everest; Arctic Metagas</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>Condor LNG; CCH LNG; Methane Lydon Volney</t>
+          <t>Condor LNG; CCH LNG; LNG Soars; Methane Lydon Volney</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
@@ -23400,14 +23400,14 @@
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="7" t="inlineStr">
-        <is>
-          <t>Kool Baltic; SCF Melampus</t>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>Cool Baltic; SCF Melampus</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/3928, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/3928, https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -23950,10 +23950,14 @@
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Hull H1799A (Hudong)</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="inlineStr"/>
+          <t>Hull H1799A (Hudong); Fath Al Khair</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
           <t>Hull H1799A</t>
@@ -29500,6 +29504,374 @@
       <c r="AR161" s="2" t="inlineStr"/>
       <c r="AS161" s="2" t="inlineStr"/>
       <c r="AT161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>9895238</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>Vivirt City LNG</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>Vivit City LNG</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M162" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O162" s="4" t="inlineStr">
+        <is>
+          <t>H-Line Shipping</t>
+        </is>
+      </c>
+      <c r="P162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr"/>
+      <c r="R162" s="2" t="inlineStr"/>
+      <c r="S162" s="4" t="inlineStr">
+        <is>
+          <t>HD Hyundai Heavy Industries</t>
+        </is>
+      </c>
+      <c r="T162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U162" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="V162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hd.com/en/main</t>
+        </is>
+      </c>
+      <c r="W162" s="4" t="inlineStr">
+        <is>
+          <t>35.51613</t>
+        </is>
+      </c>
+      <c r="X162" s="4" t="inlineStr">
+        <is>
+          <t>129.4383</t>
+        </is>
+      </c>
+      <c r="Y162" s="4" t="inlineStr">
+        <is>
+          <t>GC8Q+M6 Ulsan</t>
+        </is>
+      </c>
+      <c r="Z162" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB162" s="4" t="inlineStr">
+        <is>
+          <t>174000</t>
+        </is>
+      </c>
+      <c r="AC162" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE162" s="4" t="inlineStr">
+        <is>
+          <t>membrane</t>
+        </is>
+      </c>
+      <c r="AF162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AG162" s="4" t="inlineStr">
+        <is>
+          <t>conventional</t>
+        </is>
+      </c>
+      <c r="AH162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AI162" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK162" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="AL162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM162" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN162" s="2" t="inlineStr"/>
+      <c r="AO162" s="2" t="inlineStr"/>
+      <c r="AP162" s="2" t="inlineStr"/>
+      <c r="AQ162" s="2" t="inlineStr"/>
+      <c r="AR162" s="2" t="inlineStr"/>
+      <c r="AS162" s="2" t="inlineStr"/>
+      <c r="AT162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>9250725</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Hongkong</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>Ergy</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>https://www.vesseltracker.com/en/Ships/Ergy-9250725.html, https://www.shipvault.com/ships/116466, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116466</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M163" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O163" s="4" t="inlineStr">
+        <is>
+          <t>Energy Sinokor Merchant Marine</t>
+        </is>
+      </c>
+      <c r="P163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr"/>
+      <c r="R163" s="2" t="inlineStr"/>
+      <c r="S163" s="4" t="inlineStr">
+        <is>
+          <t>Hanwha Ocean</t>
+        </is>
+      </c>
+      <c r="T163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U163" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="V163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+        </is>
+      </c>
+      <c r="W163" s="4" t="inlineStr">
+        <is>
+          <t>34.87385</t>
+        </is>
+      </c>
+      <c r="X163" s="4" t="inlineStr">
+        <is>
+          <t>128.6966</t>
+        </is>
+      </c>
+      <c r="Y163" s="4" t="inlineStr">
+        <is>
+          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="Z163" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB163" s="4" t="inlineStr">
+        <is>
+          <t>140500</t>
+        </is>
+      </c>
+      <c r="AC163" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE163" s="4" t="inlineStr">
+        <is>
+          <t>membrane</t>
+        </is>
+      </c>
+      <c r="AF163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AG163" s="4" t="inlineStr">
+        <is>
+          <t>conventional</t>
+        </is>
+      </c>
+      <c r="AH163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AI163" s="4" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
+      <c r="AJ163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK163" s="4" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="AL163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM163" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN163" s="2" t="inlineStr"/>
+      <c r="AO163" s="2" t="inlineStr"/>
+      <c r="AP163" s="2" t="inlineStr"/>
+      <c r="AQ163" s="2" t="inlineStr"/>
+      <c r="AR163" s="2" t="inlineStr"/>
+      <c r="AS163" s="2" t="inlineStr"/>
+      <c r="AT163" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29512,7 +29884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F240"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -31798,7 +32170,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>184</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -31808,22 +32180,22 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Hull 3386 (HDHHI)</t>
+          <t>Hull 3385 (HDHHI)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/458164</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/458163</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3386 (HDHHI)'; the row is renamed 'Umm Wishah' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3385 (HDHHI)'; the row is renamed 'Barzan' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -31845,12 +32217,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/458164</t>
+          <t>https://www.shipvault.com/ships/458164</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -31862,7 +32234,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -31872,22 +32244,22 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Hull 3395 (HDHHI)</t>
+          <t>Hull 3386 (HDHHI)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/459079</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/458164</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3395 (HDHHI)'; the row is renamed 'Al Zuwair' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3386 (HDHHI)'; the row is renamed 'Umm Wishah' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -31909,12 +32281,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459079</t>
+          <t>https://www.shipvault.com/ships/459079</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -31926,7 +32298,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -31936,22 +32308,22 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Hull 3396 (HDHHI)</t>
+          <t>Hull 3395 (HDHHI)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/459080</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459079</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3396 (HDHHI)'; the row is renamed 'Sharq' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3395 (HDHHI)'; the row is renamed 'Al Zuwair' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -31973,12 +32345,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459080</t>
+          <t>https://www.shipvault.com/ships/459080</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -31990,7 +32362,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -32000,22 +32372,22 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Hull 3398 (HDHHI)</t>
+          <t>Hull 3396 (HDHHI)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/459082</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459080</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3398 (HDHHI)'; the row is renamed 'Halwan' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3396 (HDHHI)'; the row is renamed 'Sharq' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32037,12 +32409,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459082</t>
+          <t>https://www.shipvault.com/ships/459082</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -32054,7 +32426,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>192</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -32064,22 +32436,22 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Hull 3399 (HDHHI)</t>
+          <t>Hull 3398 (HDHHI)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/459083</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459082</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3399 (HDHHI)'; the row is renamed 'Al Thumaid' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3398 (HDHHI)'; the row is renamed 'Halwan' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32101,12 +32473,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459083</t>
+          <t>https://www.shipvault.com/ships/459083</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -32118,7 +32490,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -32128,22 +32500,22 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Hull 3400 (HDHHI)</t>
+          <t>Hull 3399 (HDHHI)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/459084</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459083</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3400 (HDHHI)'; the row is renamed 'Al Mazrooah' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3399 (HDHHI)'; the row is renamed 'Al Thumaid' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32165,12 +32537,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459084</t>
+          <t>https://www.shipvault.com/ships/459084</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -32182,7 +32554,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -32192,22 +32564,22 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Hull 3401 (HDHHI)</t>
+          <t>Hull 3400 (HDHHI)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/459085</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459084</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3401 (HDHHI)'; the row is renamed 'Qaffal' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3400 (HDHHI)'; the row is renamed 'Al Mazrooah' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32229,12 +32601,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459085</t>
+          <t>https://www.shipvault.com/ships/459085</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -32246,7 +32618,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>195</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -32256,22 +32628,22 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Hull 3407 (HDHHI)</t>
+          <t>Hull 3401 (HDHHI)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/460369</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/459085</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3407 (HDHHI)'; the row is renamed 'Excelerate Acadia' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3401 (HDHHI)'; the row is renamed 'Qaffal' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32293,12 +32665,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/460369</t>
+          <t>https://www.shipvault.com/ships/460369</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -32310,7 +32682,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -32320,22 +32692,22 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Hull 8182 (HSHI)</t>
+          <t>Hull 3407 (HDHHI)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/428603</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/460369</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 8182 (HSHI)'; the row is renamed 'Parthenon LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3407 (HDHHI)'; the row is renamed 'Excelerate Acadia' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32357,12 +32729,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/428603</t>
+          <t>https://www.shipvault.com/ships/428603</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -32374,7 +32746,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -32384,22 +32756,22 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Hull 8188 (HSHI)</t>
+          <t>Hull 8182 (HSHI)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/456920</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/428603</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 8188 (HSHI)'; the row is renamed 'Puteri Selangor' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 8182 (HSHI)'; the row is renamed 'Parthenon LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32421,12 +32793,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/456920</t>
+          <t>https://www.shipvault.com/ships/456920</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -32438,7 +32810,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>232</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -32448,22 +32820,22 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Hull 8189 (HSHI)</t>
+          <t>Hull 8188 (HSHI)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/456921</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/456920</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 8189 (HSHI)'; the row is renamed 'Puteri Terengganu' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 8188 (HSHI)'; the row is renamed 'Puteri Selangor' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32485,12 +32857,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/456921</t>
+          <t>https://www.shipvault.com/ships/456921</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -32502,7 +32874,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -32512,22 +32884,22 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Hull 8200 (HSHI)</t>
+          <t>Hull 8189 (HSHI)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/458170</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/456921</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 8200 (HSHI)'; the row is renamed 'Olympus LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 8189 (HSHI)'; the row is renamed 'Puteri Terengganu' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32549,12 +32921,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/458170</t>
+          <t>https://www.shipvault.com/ships/458170</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -32566,7 +32938,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>235</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -32576,22 +32948,22 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Hull 8201 (HSHI)</t>
+          <t>Hull 8200 (HSHI)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/458171</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/458170</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 8201 (HSHI)'; the row is renamed 'Frontier LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 8200 (HSHI)'; the row is renamed 'Olympus LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32613,12 +32985,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/458171</t>
+          <t>https://www.shipvault.com/ships/458171</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -32630,7 +33002,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -32640,22 +33012,22 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Hull 8204 (HSHI)</t>
+          <t>Hull 8201 (HSHI)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/461955</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/458171</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 8204 (HSHI)'; the row is renamed 'Muscat LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 8201 (HSHI)'; the row is renamed 'Frontier LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32677,12 +33049,12 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461955</t>
+          <t>https://www.shipvault.com/ships/461955</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -32694,7 +33066,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>237</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -32704,22 +33076,22 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Hull 8205 (HSHI)</t>
+          <t>Hull 8204 (HSHI)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/461956</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461955</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 8205 (HSHI)'; the row is renamed 'Musandam LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 8204 (HSHI)'; the row is renamed 'Muscat LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32741,12 +33113,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461956</t>
+          <t>https://www.shipvault.com/ships/461956</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -32758,7 +33130,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>238</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -32768,22 +33140,22 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Hull H1800A (Hudong); QatarGas LNG 36</t>
+          <t>Hull 8205 (HSHI)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/462939</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461956</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull H1800A'; the row is renamed 'Mihzem' by 2026-09-17_0421ET_fix_delivery_rollforward; plus IGU 2026 prints 'Mizhem (ex-QatarGas LNG 36 (2563))'; IGU's hull tag (2563) not checked against the row</t>
+          <t>former Name 'Hull 8205 (HSHI)'; the row is renamed 'Musandam LNG' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -32805,12 +33177,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462939</t>
+          <t>https://www.shipvault.com/ships/462939</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -32837,12 +33209,12 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462939</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -32854,7 +33226,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>264</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -32864,22 +33236,22 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Hull H1801A (Hudong); QatarGas LNG 52</t>
+          <t>Hull H1800A (Hudong); QatarGas LNG 36</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/462940</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull H1801A'; the row is renamed 'Idd Al Shargi' by 2026-09-17_0421ET_fix_delivery_rollforward; plus IGU 2026 prints 'IDD Al Shargi (ex-QatarGas LNG 52 (1801A))'; IGU's hull tag (1801A) not checked against the row</t>
+          <t>former Name 'Hull H1800A'; the row is renamed 'Mihzem' by 2026-09-17_0421ET_fix_delivery_rollforward; plus IGU 2026 prints 'Mizhem (ex-QatarGas LNG 36 (2563))'; IGU's hull tag (2563) not checked against the row</t>
         </is>
       </c>
     </row>
@@ -32901,12 +33273,12 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462940</t>
+          <t>https://www.shipvault.com/ships/462940</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -32933,12 +33305,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462940</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -32950,7 +33322,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>265</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -32960,22 +33332,22 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Hull H1909A (Hudong)</t>
+          <t>Hull H1801A (Hudong); QatarGas LNG 52</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/467899</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull H1909A'; the row is renamed 'Tianshan' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull H1801A'; the row is renamed 'Idd Al Shargi' by 2026-09-17_0421ET_fix_delivery_rollforward; plus IGU 2026 prints 'IDD Al Shargi (ex-QatarGas LNG 52 (1801A))'; IGU's hull tag (1801A) not checked against the row</t>
         </is>
       </c>
     </row>
@@ -32997,12 +33369,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/467899</t>
+          <t>https://www.shipvault.com/ships/467899</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -33014,7 +33386,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -33024,22 +33396,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Hull YZJ2022-1475</t>
+          <t>Hull H1909A (Hudong)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/475022</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/467899</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull YZJ2022-1475'; the row is renamed 'Yangze LNG 01' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull H1909A'; the row is renamed 'Tianshan' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33061,12 +33433,12 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/475022</t>
+          <t>https://www.shipvault.com/ships/475022</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -33078,7 +33450,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -33088,22 +33460,22 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Hull 2317 (SHI)</t>
+          <t>Hull YZJ2022-1475</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/432643</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/475022</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2317 (SHI)'; the row is renamed 'Mediterranean Success' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull YZJ2022-1475'; the row is renamed 'Yangze LNG 01' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33125,12 +33497,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/432643</t>
+          <t>https://www.shipvault.com/ships/432643</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -33142,7 +33514,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -33152,22 +33524,22 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Hull 2318 (SHI)</t>
+          <t>Hull 2317 (SHI)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/432644</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/432643</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2318 (SHI)'; the row is renamed 'Caribbean Success' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2317 (SHI)'; the row is renamed 'Mediterranean Success' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33189,12 +33561,12 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/432644</t>
+          <t>https://www.shipvault.com/ships/432644</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -33206,7 +33578,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -33216,22 +33588,22 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Hull 2582 (Hanwha)</t>
+          <t>Hull 2318 (SHI)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/470097</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/432644</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2582 (Hanwha)'; the row is renamed 'Maran Gas Poliegos' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2318 (SHI)'; the row is renamed 'Caribbean Success' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33253,12 +33625,12 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/470097</t>
+          <t>https://www.shipvault.com/ships/470097</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -33270,7 +33642,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -33280,22 +33652,22 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Hull 2687 (SHI)</t>
+          <t>Hull 2582 (Hanwha)</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/471277</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/470097</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2687 (SHI)'; the row is renamed 'Barthy Vanguard' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2582 (Hanwha)'; the row is renamed 'Maran Gas Poliegos' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33317,12 +33689,12 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/471277</t>
+          <t>https://www.shipvault.com/ships/471277</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -33334,7 +33706,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -33344,22 +33716,22 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Hull 2700 (SHI)</t>
+          <t>Hull 2687 (SHI)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479145</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/471277</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2700 (SHI)'; the row is renamed 'Al Seej' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2687 (SHI)'; the row is renamed 'Barthy Vanguard' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33381,12 +33753,12 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479145</t>
+          <t>https://www.shipvault.com/ships/479145</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -33398,7 +33770,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -33408,22 +33780,22 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Hull 3452 (HDHHI)</t>
+          <t>Hull 2700 (SHI)</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/462869</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479145</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3452 (HDHHI)'; the row is renamed 'Clean Astraeus' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2700 (SHI)'; the row is renamed 'Al Seej' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33445,12 +33817,12 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462869</t>
+          <t>https://www.shipvault.com/ships/462869</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -33462,7 +33834,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -33472,22 +33844,22 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Hull 3453 (HDHHI)</t>
+          <t>Hull 3452 (HDHHI)</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/462870</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462869</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3453 (HDHHI)'; the row is renamed 'Clean Azeus' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3452 (HDHHI)'; the row is renamed 'Clean Astraeus' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33509,12 +33881,12 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462870</t>
+          <t>https://www.shipvault.com/ships/462870</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -33526,7 +33898,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -33536,22 +33908,22 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Hull 3476 (HDHHI)</t>
+          <t>Hull 3453 (HDHHI)</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478305</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462870</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3476 (HDHHI)'; the row is renamed 'Al Ghuwair' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3453 (HDHHI)'; the row is renamed 'Clean Azeus' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33573,12 +33945,12 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478305</t>
+          <t>https://www.shipvault.com/ships/478305</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -33590,7 +33962,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -33600,22 +33972,22 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Hull 3477 (HDHHI)</t>
+          <t>Hull 3476 (HDHHI)</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478306</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478305</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3477 (HDHHI)'; the row is renamed 'Wadi Sultana' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3476 (HDHHI)'; the row is renamed 'Al Ghuwair' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33637,12 +34009,12 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478306</t>
+          <t>https://www.shipvault.com/ships/478306</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -33654,7 +34026,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -33664,22 +34036,22 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Hull 3478 (HDHHI)</t>
+          <t>Hull 3477 (HDHHI)</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478307</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478306</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3478 (HDHHI)'; the row is renamed 'Lesha' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3477 (HDHHI)'; the row is renamed 'Wadi Sultana' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33701,12 +34073,12 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478307</t>
+          <t>https://www.shipvault.com/ships/478307</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -33718,7 +34090,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -33728,22 +34100,22 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Hull 3479 (HDHHI)</t>
+          <t>Hull 3478 (HDHHI)</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478308</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478307</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3479 (HDHHI)'; the row is renamed 'Al Jazi' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3478 (HDHHI)'; the row is renamed 'Lesha' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33765,12 +34137,12 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478308</t>
+          <t>https://www.shipvault.com/ships/478308</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -33782,7 +34154,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -33792,22 +34164,22 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Hull 3480 (HDHHI)</t>
+          <t>Hull 3479 (HDHHI)</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478309</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478308</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3480 (HDHHI)'; the row is renamed 'Al Mashrab' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3479 (HDHHI)'; the row is renamed 'Al Jazi' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33829,12 +34201,12 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478309</t>
+          <t>https://www.shipvault.com/ships/478309</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -33846,7 +34218,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -33856,22 +34228,22 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Hull 3481 (HDHHI)</t>
+          <t>Hull 3480 (HDHHI)</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478310</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478309</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3481 (HDHHI)'; the row is renamed 'Al Mirzam' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3480 (HDHHI)'; the row is renamed 'Al Mashrab' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33893,12 +34265,12 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478310</t>
+          <t>https://www.shipvault.com/ships/478310</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -33910,7 +34282,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -33920,22 +34292,22 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Hull 3482 (HDHHI)</t>
+          <t>Hull 3481 (HDHHI)</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478311</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478310</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3482 (HDHHI)'; the row is renamed 'Maqdeem' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3481 (HDHHI)'; the row is renamed 'Al Mirzam' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -33957,12 +34329,12 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478311</t>
+          <t>https://www.shipvault.com/ships/478311</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -33974,7 +34346,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -33984,22 +34356,22 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Hull 3483 (HDHHI)</t>
+          <t>Hull 3482 (HDHHI)</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478312</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478311</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3483 (HDHHI)'; the row is renamed 'Al Rufaa' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3482 (HDHHI)'; the row is renamed 'Maqdeem' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34021,12 +34393,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478312</t>
+          <t>https://www.shipvault.com/ships/478312</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -34038,7 +34410,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -34048,22 +34420,22 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Hull 3484 (HDHHI)</t>
+          <t>Hull 3483 (HDHHI)</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478313</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478312</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3484 (HDHHI)'; the row is renamed 'Al Nekhsh' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3483 (HDHHI)'; the row is renamed 'Al Rufaa' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34085,12 +34457,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478313</t>
+          <t>https://www.shipvault.com/ships/478313</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -34102,7 +34474,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -34112,22 +34484,22 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Hull 3485 (HDHHI)</t>
+          <t>Hull 3484 (HDHHI)</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478314</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478313</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3485 (HDHHI)'; the row is renamed "Leh'saien" by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3484 (HDHHI)'; the row is renamed 'Al Nekhsh' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34149,12 +34521,12 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478314</t>
+          <t>https://www.shipvault.com/ships/478314</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -34166,7 +34538,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -34176,22 +34548,22 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Hull 3486 (HDHHI)</t>
+          <t>Hull 3485 (HDHHI)</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478315</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478314</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3486 (HDHHI)'; the row is renamed "Le'shara" by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3485 (HDHHI)'; the row is renamed "Leh'saien" by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34213,12 +34585,12 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478315</t>
+          <t>https://www.shipvault.com/ships/478315</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -34230,7 +34602,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -34240,22 +34612,22 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Hull 3487 (HDHHI)</t>
+          <t>Hull 3486 (HDHHI)</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478316</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478315</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3487 (HDHHI)'; the row is renamed 'Librega' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3486 (HDHHI)'; the row is renamed "Le'shara" by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34277,12 +34649,12 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478316</t>
+          <t>https://www.shipvault.com/ships/478316</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -34294,7 +34666,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -34304,22 +34676,22 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Hull 3488 (HDHHI)</t>
+          <t>Hull 3487 (HDHHI)</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478317</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478316</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3488 (HDHHI)'; the row is renamed 'Eshairej' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3487 (HDHHI)'; the row is renamed 'Librega' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34341,12 +34713,12 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478317</t>
+          <t>https://www.shipvault.com/ships/478317</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -34358,7 +34730,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -34368,22 +34740,22 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Hull 3489 (HDHHI)</t>
+          <t>Hull 3488 (HDHHI)</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478318</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478317</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3489 (HDHHI)'; the row is renamed 'Mneefa' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3488 (HDHHI)'; the row is renamed 'Eshairej' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34405,12 +34777,12 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478318</t>
+          <t>https://www.shipvault.com/ships/478318</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -34422,7 +34794,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -34432,22 +34804,22 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Hull 3490 (HDHHI)</t>
+          <t>Hull 3489 (HDHHI)</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478319</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478318</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3490 (HDHHI)'; the row is renamed 'Ezhara' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3489 (HDHHI)'; the row is renamed 'Mneefa' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34469,12 +34841,12 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478319</t>
+          <t>https://www.shipvault.com/ships/478319</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -34486,7 +34858,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -34496,22 +34868,22 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Hull H1794A (Hudong)</t>
+          <t>Hull 3490 (HDHHI)</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/462933</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478319</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull H1794A'; the row is renamed 'Al Sabsab' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3490 (HDHHI)'; the row is renamed 'Ezhara' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34533,12 +34905,12 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462933</t>
+          <t>https://www.shipvault.com/ships/462933</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -34550,7 +34922,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -34560,22 +34932,22 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Hull 2585 (Hanwha)</t>
+          <t>Hull H1794A (Hudong)</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476659</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462933</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2585 (Hanwha)'; the row is renamed 'Al Nasraniya' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull H1794A'; the row is renamed 'Al Sabsab' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34597,12 +34969,12 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476659</t>
+          <t>https://www.shipvault.com/ships/476659</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -34614,7 +34986,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -34624,22 +34996,22 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Hull 2586 (Hanwha)</t>
+          <t>Hull 2585 (Hanwha)</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476660</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476659</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2586 (Hanwha)'; the row is renamed 'Al Yousifiya' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2585 (Hanwha)'; the row is renamed 'Al Nasraniya' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34661,12 +35033,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660</t>
+          <t>https://www.shipvault.com/ships/476660</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -34678,7 +35050,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -34688,22 +35060,22 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Hull 2587 (Hanwha)</t>
+          <t>Hull 2586 (Hanwha)</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476661</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2587 (Hanwha)'; the row is renamed 'Athba' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2586 (Hanwha)'; the row is renamed 'Al Yousifiya' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34725,12 +35097,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661</t>
+          <t>https://www.shipvault.com/ships/476661</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -34742,7 +35114,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -34752,22 +35124,22 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Hull 2588 (Hanwha)</t>
+          <t>Hull 2587 (Hanwha)</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476662</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2588 (Hanwha)'; the row is renamed 'E Qab' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2587 (Hanwha)'; the row is renamed 'Athba' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34789,12 +35161,12 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662</t>
+          <t>https://www.shipvault.com/ships/476662</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -34806,7 +35178,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -34816,22 +35188,22 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Hull 2589 (Hanwha)</t>
+          <t>Hull 2588 (Hanwha)</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478215</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2589 (Hanwha)'; the row is renamed 'Ghash Sham' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2588 (Hanwha)'; the row is renamed 'E Qab' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34853,12 +35225,12 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215</t>
+          <t>https://www.shipvault.com/ships/478215</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -34870,7 +35242,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -34880,22 +35252,22 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Hull 2590 (Hanwha)</t>
+          <t>Hull 2589 (Hanwha)</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478216</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2590 (Hanwha)'; the row is renamed 'Al Egdah' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2589 (Hanwha)'; the row is renamed 'Ghash Sham' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34917,12 +35289,12 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216</t>
+          <t>https://www.shipvault.com/ships/478216</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -34934,7 +35306,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -34944,22 +35316,22 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Hull 2591 (Hanwha)</t>
+          <t>Hull 2590 (Hanwha)</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478217</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2591 (Hanwha)'; the row is renamed 'Al Khbaib' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2590 (Hanwha)'; the row is renamed 'Al Egdah' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -34981,12 +35353,12 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217</t>
+          <t>https://www.shipvault.com/ships/478217</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -34998,7 +35370,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -35008,22 +35380,22 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Hull 2592 (Hanwha)</t>
+          <t>Hull 2591 (Hanwha)</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478218</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2592 (Hanwha)'; the row is renamed 'Khowzan' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2591 (Hanwha)'; the row is renamed 'Al Khbaib' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -35045,12 +35417,12 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218</t>
+          <t>https://www.shipvault.com/ships/478218</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -35062,7 +35434,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -35072,22 +35444,22 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Hull 2694 (SHI)</t>
+          <t>Hull 2592 (Hanwha)</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479139</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2694 (SHI)'; the row is renamed 'Lekhraib' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2592 (Hanwha)'; the row is renamed 'Khowzan' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -35109,12 +35481,12 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139</t>
+          <t>https://www.shipvault.com/ships/479139</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -35126,7 +35498,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -35136,22 +35508,22 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Hull 2696 (SHI)</t>
+          <t>Hull 2694 (SHI)</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479141</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2696 (SHI)'; the row is renamed 'Wadi Al Askar' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2694 (SHI)'; the row is renamed 'Lekhraib' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -35173,12 +35545,12 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141</t>
+          <t>https://www.shipvault.com/ships/479141</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -35190,7 +35562,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -35200,22 +35572,22 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Hull 2699 (SHI)</t>
+          <t>Hull 2696 (SHI)</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479144</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2699 (SHI)'; the row is renamed 'Al Shaheen' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2696 (SHI)'; the row is renamed 'Wadi Al Askar' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -35237,12 +35609,12 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144</t>
+          <t>https://www.shipvault.com/ships/479144</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -35254,7 +35626,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -35264,22 +35636,22 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Hull 2706 (SHI)</t>
+          <t>Hull 2699 (SHI)</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479151</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 2706 (SHI)'; the row is renamed 'Al Nouf' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2699 (SHI)'; the row is renamed 'Al Shaheen' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -35301,12 +35673,12 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151</t>
+          <t>https://www.shipvault.com/ships/479151</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -35318,7 +35690,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -35328,22 +35700,22 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Hull 3491 (HDHHI)</t>
+          <t>Hull 2706 (SHI)</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478320</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3491 (HDHHI)'; the row is renamed 'Izghawa' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 2706 (SHI)'; the row is renamed 'Al Nouf' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -35365,12 +35737,12 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320</t>
+          <t>https://www.shipvault.com/ships/478320</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -35382,7 +35754,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>222</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -35392,22 +35764,22 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Hull 3492 (HDHHI)</t>
+          <t>Hull 3491 (HDHHI)</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478321</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Hull 3492 (HDHHI)'; the row is renamed "Al Wa'ab" by 2026-09-17_0421ET_fix_delivery_rollforward</t>
+          <t>former Name 'Hull 3491 (HDHHI)'; the row is renamed 'Izghawa' by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -35429,12 +35801,12 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321</t>
+          <t>https://www.shipvault.com/ships/478321</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -35446,7 +35818,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -35456,22 +35828,22 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Karmol LNGT Powership Antarctica; Karadeniz LNGT Antarctica; Northwest Sanderling</t>
+          <t>Hull 3492 (HDHHI)</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://www.lngindustry.com/regasification/28052025/karpowership-celebrates-fsru-undocking-with-karmol-and-seatrium/</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Karmol LNGT Powership Antarctica' (lngindustry.com, 2025-05-28); the row is renamed 'LNGT Antarctica' by 2026-09-17_1654ET_fix_igu2026_sourced; IGU 2026 prints 'Karadeniz LNGT Antarctica (ex-Northwest Sanderling)' — both IGU names carried here (Baird 2026-09-18)</t>
+          <t>former Name 'Hull 3492 (HDHHI)'; the row is renamed "Al Wa'ab" by 2026-09-17_0421ET_fix_delivery_rollforward</t>
         </is>
       </c>
     </row>
@@ -35493,12 +35865,12 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.lngindustry.com/regasification/28052025/karpowership-celebrates-fsru-undocking-with-karmol-and-seatrium/</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -35542,7 +35914,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -35552,7 +35924,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>LNGT Americas; Northwest Stormpetrel</t>
+          <t>Karmol LNGT Powership Antarctica; Karadeniz LNGT Antarctica; Northwest Sanderling</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -35567,14 +35939,14 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>former Name 'LNGT Americas'; the row is renamed 'Karadeniz LNGT Americas' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Americas (ex-Northwest Stormpetrel)'</t>
+          <t>former Name 'Karmol LNGT Powership Antarctica' (lngindustry.com, 2025-05-28); the row is renamed 'LNGT Antarctica' by 2026-09-17_1654ET_fix_igu2026_sourced; IGU 2026 prints 'Karadeniz LNGT Antarctica (ex-Northwest Sanderling)' — both IGU names carried here (Baird 2026-09-18)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>811</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -35584,7 +35956,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Puteri Intan</t>
+          <t>LNGT Americas; Karadeniz LNGT Americas; Northwest Stormpetrel</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -35594,19 +35966,19 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Puteri Intan'; the row is renamed 'American Energy' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'LNGT Americas' (no ref prints it — the backend's own published value); IGU 2026 prints 'Karadeniz LNGT Americas (ex-Northwest Stormpetrel)' — IGU's name is carried here, not as the Name [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>811</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -35616,7 +35988,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>KLNGTP Black Sea; Portovenere; LNG Portovenere</t>
+          <t>LNGT Americas; Karadeniz LNGT Americas; Northwest Stormpetrel</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -35626,19 +35998,19 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>former Name 'KLNGTP Black Sea'; the row is renamed 'Karadeniz LNGT Powership Black Sea' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'</t>
+          <t>former Name 'LNGT Americas' (no ref prints it — the backend's own published value); IGU 2026 prints 'Karadeniz LNGT Americas (ex-Northwest Stormpetrel)' — IGU's name is carried here, not as the Name [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>971</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -35648,7 +36020,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>KLNGTP Black Sea; Portovenere; LNG Portovenere</t>
+          <t>Puteri Intan</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -35658,19 +36030,19 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>former Name 'KLNGTP Black Sea'; the row is renamed 'Karadeniz LNGT Powership Black Sea' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Black Sea (ex-Portovenere / ex-LNG Portovenere)'</t>
+          <t>former Name 'Puteri Intan'; the row is renamed 'American Energy' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>726</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -35680,7 +36052,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>KLNGTP Marmara; Lerici; LNG Lerici</t>
+          <t>Karadeniz LNGT Powership Black Sea; Portovenere; LNG Portovenere</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -35690,19 +36062,19 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>former Name 'KLNGTP Marmara'; the row is renamed 'Karadeniz LNGT Powership Marmara' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'</t>
+          <t>Name stays 'KLNGTP Black Sea' (vesseltracker.com live AIS name); the long form IGU 2026 and marinetraffic.org print is carried here (Baird 2026-09-21), with IGU's (ex-…) names [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>726</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -35712,29 +36084,29 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>KLNGTP Marmara; Lerici; LNG Lerici</t>
+          <t>Karadeniz LNGT Powership Black Sea; Portovenere; LNG Portovenere</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/KARADENIZ-LNGT-POWERSHIP-BLACK-SEA/9064073/352004132</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>former Name 'KLNGTP Marmara'; the row is renamed 'Karadeniz LNGT Powership Marmara' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'; plus IGU 2026 prints 'Karadeniz LNGT Powership Marmara (ex-Lerici / ex-LNG Lerici)'</t>
+          <t>Name stays 'KLNGTP Black Sea' (vesseltracker.com live AIS name); the long form IGU 2026 and marinetraffic.org print is carried here (Baird 2026-09-21), with IGU's (ex-…) names [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>726</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -35744,29 +36116,29 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Seapeak Hispania</t>
+          <t>Karadeniz LNGT Powership Black Sea; Portovenere; LNG Portovenere</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/115017</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Seapeak Hispania'; the row is renamed 'Seapeak Jupiter' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>Name stays 'KLNGTP Black Sea' (vesseltracker.com live AIS name); the long form IGU 2026 and marinetraffic.org print is carried here (Baird 2026-09-21), with IGU's (ex-…) names [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>726</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -35776,29 +36148,29 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Seapeak Hispania</t>
+          <t>Karadeniz LNGT Powership Black Sea; Portovenere; LNG Portovenere</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/115017</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Seapeak Hispania'; the row is renamed 'Seapeak Jupiter' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>Name stays 'KLNGTP Black Sea' (vesseltracker.com live AIS name); the long form IGU 2026 and marinetraffic.org print is carried here (Baird 2026-09-21), with IGU's (ex-…) names [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>727</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -35808,29 +36180,29 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Energy Frontier</t>
+          <t>Karadeniz LNGT Powership Marmara; Lerici; LNG Lerici</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/116125</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Energy Frontier'; the row is renamed 'Arunika Jaya' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>Name stays 'KLNGTP Marmara' (vesseltracker.com live AIS name); the long form IGU 2026 and marinetraffic.org print is carried here (Baird 2026-09-21), with IGU's (ex-…) names [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>727</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -35840,29 +36212,29 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Energy Frontier</t>
+          <t>Karadeniz LNGT Powership Marmara; Lerici; LNG Lerici</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116125</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/KARADENIZ-LNGT-POWERSHIP-MARMARA/9064085/352004078</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Energy Frontier'; the row is renamed 'Arunika Jaya' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>Name stays 'KLNGTP Marmara' (vesseltracker.com live AIS name); the long form IGU 2026 and marinetraffic.org print is carried here (Baird 2026-09-21), with IGU's (ex-…) names [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>727</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -35872,29 +36244,29 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Golar Arctic</t>
+          <t>Karadeniz LNGT Powership Marmara; Lerici; LNG Lerici</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/116640</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Golar Arctic'; the row is renamed 'SC Serenity' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>Name stays 'KLNGTP Marmara' (vesseltracker.com live AIS name); the long form IGU 2026 and marinetraffic.org print is carried here (Baird 2026-09-21), with IGU's (ex-…) names [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>727</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -35904,29 +36276,29 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Golar Arctic</t>
+          <t>Karadeniz LNGT Powership Marmara; Lerici; LNG Lerici</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116640</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Golar Arctic'; the row is renamed 'SC Serenity' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>Name stays 'KLNGTP Marmara' (vesseltracker.com live AIS name); the long form IGU 2026 and marinetraffic.org print is carried here (Baird 2026-09-21), with IGU's (ex-…) names [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -35936,29 +36308,29 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Metagas Everest</t>
+          <t>Seapeak Hispania; Seapeak Jupiter</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.shipvault.com/ships/115017</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Metagas Everest'; the row is renamed 'Arctic Metagas' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Seapeak Hispania'; the row is renamed 'Gas Polaris'; IGU 2026's 'Seapeak Jupiter' carried here [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -35968,29 +36340,29 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>LNG River Orashi</t>
+          <t>Seapeak Hispania; Seapeak Jupiter</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/115017</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>former Name 'LNG River Orashi'; the row is renamed 'Gas Garuda' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Seapeak Hispania'; the row is renamed 'Gas Polaris'; IGU 2026's 'Seapeak Jupiter' carried here [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -36000,7 +36372,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>LNG Pioneer; Pioneer Spirit</t>
+          <t>Seapeak Hispania; Seapeak Jupiter</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -36010,19 +36382,19 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Pioneer Spirit'; the row is renamed 'Arctic Pioneer' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Seapeak Hispania'; the row is renamed 'Gas Polaris'; IGU 2026's 'Seapeak Jupiter' carried here [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>562</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -36032,29 +36404,29 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Condor LNG; CCH LNG; Methane Lydon Volney</t>
+          <t>Energy Frontier</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.shipvault.com/ships/116125</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>former Name 'CCH LNG'; the row is renamed 'LNG Soars' by 2026-09-17_1654ET_fix_igu2026_sourced — no ref on hand prints the former name (backend's own published value); held; plus IGU 2026 prints 'LNG Soars (ex-Methane Lydon Volney)'</t>
+          <t>former Name 'Energy Frontier'; the row is renamed 'Arunika Jaya' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>562</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -36064,29 +36436,29 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Methane Heather Sally</t>
+          <t>Energy Frontier</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116125</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Methane Heather Sally'; the row is renamed 'Shandong Redwood' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Energy Frontier'; the row is renamed 'Arunika Jaya' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>648</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -36096,29 +36468,29 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Golar Tundra</t>
+          <t>Golar Arctic</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+          <t>https://www.shipvault.com/ships/116640</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Golar Tundra'; the row is renamed 'Italis LNG' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'Golar Arctic'; the row is renamed 'SC Serenity' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>648</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -36128,29 +36500,29 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Kool Baltic; SCF Melampus</t>
+          <t>Golar Arctic</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/3928</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116640</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Kool Baltic'; the row is renamed 'Cool Baltic' by 2026-09-17_1654ET_fix_igu2026_sourced; plus IGU 2026 prints 'Cool Baltic (ex-SCF Melampus)'</t>
+          <t>former Name 'Golar Arctic'; the row is renamed 'SC Serenity' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>866</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -36160,29 +36532,29 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Kool Baltic; SCF Melampus</t>
+          <t>Metagas Everest; Arctic Metagas</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/3928</t>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Kool Baltic'; the row is renamed 'Cool Baltic' by 2026-09-17_1654ET_fix_igu2026_sourced; plus IGU 2026 prints 'Cool Baltic (ex-SCF Melampus)'</t>
+          <t>former Name 'Metagas Everest'; the row is renamed 'Arctic Metagaz'; IGU 2026's spelling 'Arctic Metagas' carried here [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>866</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -36192,7 +36564,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Kool Baltic; SCF Melampus</t>
+          <t>Metagas Everest; Arctic Metagas</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -36207,14 +36579,14 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>former Name 'Kool Baltic'; the row is renamed 'Cool Baltic' by 2026-09-17_1654ET_fix_igu2026_sourced; plus IGU 2026 prints 'Cool Baltic (ex-SCF Melampus)'</t>
+          <t>former Name 'Metagas Everest'; the row is renamed 'Arctic Metagaz'; IGU 2026's spelling 'Arctic Metagas' carried here [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>801</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -36224,7 +36596,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>SCF La Perouse</t>
+          <t>LNG River Orashi</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -36239,14 +36611,14 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>former Name 'SCF La Perouse'; the row is renamed 'La Perouse' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
+          <t>former Name 'LNG River Orashi'; the row is renamed 'Gas Garuda' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>958</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -36256,7 +36628,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Hull 3342 (HDHHI)</t>
+          <t>LNG Pioneer; Pioneer Spirit</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -36266,19 +36638,19 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Apostolos (ex-Hyundai 3342)' — hull-number former name written as the QC §2 placeholder 'Hull 3342 (HDHHI)'</t>
+          <t>former Name 'Pioneer Spirit'; the row is renamed 'Arctic Pioneer' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -36288,7 +36660,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Hull 3341 (HDHHI)</t>
+          <t>Condor LNG; CCH LNG; LNG Soars; Methane Lydon Volney</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -36303,14 +36675,14 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Assos (ex-3341)' — hull-number former name written as the QC §2 placeholder 'Hull 3341 (HDHHI)'</t>
+          <t>former Name 'CCH LNG' (no ref prints it — the backend's own published value); the row is renamed 'LNG Scorpio'; IGU 2026 prints 'LNG Soars (ex-Methane Lydon Volney)' — both carried here [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -36320,7 +36692,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Hull 2635 (SHI)</t>
+          <t>Condor LNG; CCH LNG; LNG Soars; Methane Lydon Volney</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -36335,14 +36707,14 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Athos LNG (ex-Samsung 2635)' — hull-number former name written as the QC §2 placeholder 'Hull 2635 (SHI)'</t>
+          <t>former Name 'CCH LNG' (no ref prints it — the backend's own published value); the row is renamed 'LNG Scorpio'; IGU 2026 prints 'LNG Soars (ex-Methane Lydon Volney)' — both carried here [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>869</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -36352,7 +36724,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Hull 2584 (SHI)</t>
+          <t>Methane Heather Sally</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -36367,14 +36739,14 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Celsius Greenwich (ex-2584)' — hull-number former name written as the QC §2 placeholder 'Hull 2584 (SHI)'</t>
+          <t>former Name 'Methane Heather Sally'; the row is renamed 'Shandong Redwood' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>649</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -36384,7 +36756,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Hull 3293 (HDHHI)</t>
+          <t>Golar Tundra</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -36399,14 +36771,14 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Clean Future (ex-3293)' — hull-number former name written as the QC §2 placeholder 'Hull 3293 (HDHHI)'</t>
+          <t>former Name 'Golar Tundra'; the row is renamed 'Italis LNG' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>729</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -36416,7 +36788,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Hull 1881A (Hudong)</t>
+          <t>Cool Baltic; SCF Melampus</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -36426,19 +36798,19 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Greenergy Pearl (ex-Hudong-Zhonghua H1881A)' — hull-number former name written as the QC §2 placeholder 'Hull 1881A (Hudong)'</t>
+          <t>Name stays 'Kool Baltic' (shipvault, marinetraffic.org, vesseltracker.com); IGU 2026 prints 'Cool Baltic (ex-SCF Melampus)' — probably IGU's misspelling; reject to leave it out [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>729</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -36448,7 +36820,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Hull 1792A (Hudong)</t>
+          <t>Cool Baltic; SCF Melampus</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -36463,14 +36835,14 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Hlaitan (ex-H1792A)' — hull-number former name written as the QC §2 placeholder 'Hull 1792A (Hudong)'</t>
+          <t>Name stays 'Kool Baltic' (shipvault, marinetraffic.org, vesseltracker.com); IGU 2026 prints 'Cool Baltic (ex-SCF Melampus)' — probably IGU's misspelling; reject to leave it out [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>993</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -36480,7 +36852,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>LNG Unity; Provalys</t>
+          <t>SCF La Perouse</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -36490,19 +36862,19 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Karadeniz LNGT Powership Anatolia (ex-LNG Unity / ex-Provalys)'; Provalys</t>
+          <t>former Name 'SCF La Perouse'; the row is renamed 'La Perouse' by 2026-09-17_1654ET_fix_igu2026_sourced</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>263</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -36512,7 +36884,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>LNG Unity; Provalys</t>
+          <t>Hull H1799A (Hudong); Fath Al Khair</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -36527,14 +36899,14 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Karadeniz LNGT Powership Anatolia (ex-LNG Unity / ex-Provalys)'; Provalys</t>
+          <t>former Name 'Hull H1799A'; the row is named 'Fat'h Al Khair'; IGU 2026's spelling 'Fath Al Khair' carried here [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>385</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -36544,7 +36916,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Dwiputra</t>
+          <t>Hull 3342 (HDHHI)</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -36559,14 +36931,14 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Karmol LNGT Powership Africa (ex-Dwiputra)'</t>
+          <t>IGU 2026 prints 'Apostolos (ex-Hyundai 3342)' — hull-number former name written as the QC §2 placeholder 'Hull 3342 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -36576,7 +36948,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Northwest Shearwater</t>
+          <t>Hull 3341 (HDHHI)</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -36586,19 +36958,19 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Karmol LNGT Powership Asia (ex-Northwest Shearwater)'</t>
+          <t>IGU 2026 prints 'Assos (ex-3341)' — hull-number former name written as the QC §2 placeholder 'Hull 3341 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -36608,7 +36980,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Hull 1836A (Hudong)</t>
+          <t>Hull 2635 (SHI)</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -36618,19 +36990,19 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Kongtong (ex-Hudong-Zhonghua H1836A)' — hull-number former name written as the QC §2 placeholder 'Hull 1836A (Hudong)'</t>
+          <t>IGU 2026 prints 'Athos LNG (ex-Samsung 2635)' — hull-number former name written as the QC §2 placeholder 'Hull 2635 (SHI)'</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -36640,7 +37012,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>SCF Mitre</t>
+          <t>Hull 2584 (SHI)</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -36655,14 +37027,14 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Kool Boreas (ex-SCF Mitre)'</t>
+          <t>IGU 2026 prints 'Celsius Greenwich (ex-2584)' — hull-number former name written as the QC §2 placeholder 'Hull 2584 (SHI)'</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -36672,7 +37044,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>SCF Barents</t>
+          <t>Hull 3293 (HDHHI)</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -36682,19 +37054,19 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Kool Firn (ex-SCF Barents)'</t>
+          <t>IGU 2026 prints 'Clean Future (ex-3293)' — hull-number former name written as the QC §2 placeholder 'Hull 3293 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -36704,7 +37076,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Hull 3221 (HDHHI)</t>
+          <t>Hull 1881A (Hudong)</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -36714,19 +37086,19 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'New Brave (ex-3221)' — hull-number former name written as the QC §2 placeholder 'Hull 3221 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Greenergy Pearl (ex-Hudong-Zhonghua H1881A)' — hull-number former name written as the QC §2 placeholder 'Hull 1881A (Hudong)'</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -36736,7 +37108,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Hull 3224 (HDHHI)</t>
+          <t>Hull 1792A (Hudong)</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -36751,14 +37123,14 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'New Green ST (ex-3224)' — hull-number former name written as the QC §2 placeholder 'Hull 3224 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Hlaitan (ex-H1792A)' — hull-number former name written as the QC §2 placeholder 'Hull 1792A (Hudong)'</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>719</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -36768,7 +37140,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Hull 3222 (HDHHI)</t>
+          <t>LNG Unity; Provalys</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -36783,14 +37155,14 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'New Nature (ex-3222)' — hull-number former name written as the QC §2 placeholder 'Hull 3222 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Karadeniz LNGT Powership Anatolia (ex-LNG Unity / ex-Provalys)'; Provalys</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>719</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -36800,7 +37172,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Hull 2592 (SHI)</t>
+          <t>LNG Unity; Provalys</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -36815,14 +37187,14 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Orion Spirit (ex-2592)' — hull-number former name written as the QC §2 placeholder 'Hull 2592 (SHI)'</t>
+          <t>IGU 2026 prints 'Karadeniz LNGT Powership Anatolia (ex-LNG Unity / ex-Provalys)'; Provalys</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>720</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -36832,7 +37204,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Hull 2315 (SHI)</t>
+          <t>Dwiputra</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -36842,19 +37214,19 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Pacific Success (ex-Samsung Heavy Industries 2315)' — hull-number former name written as the QC §2 placeholder 'Hull 2315 (SHI)'</t>
+          <t>IGU 2026 prints 'Karmol LNGT Powership Africa (ex-Dwiputra)'</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -36864,7 +37236,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Hull 3297 (HDHHI)</t>
+          <t>Northwest Shearwater</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -36874,19 +37246,19 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Puteri Ledang (ex-Hull 3297)' — hull-number former name written as the QC §2 placeholder 'Hull 3297 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Karmol LNGT Powership Asia (ex-Northwest Shearwater)'</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -36896,7 +37268,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Hull 3298 (HDHHI)</t>
+          <t>Hull 1836A (Hudong)</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -36906,19 +37278,19 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Puteri Mahsuri (ex-Hull 3298)' — hull-number former name written as the QC §2 placeholder 'Hull 3298 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Kongtong (ex-Hudong-Zhonghua H1836A)' — hull-number former name written as the QC §2 placeholder 'Hull 1836A (Hudong)'</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>731</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -36928,7 +37300,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Hull 3295 (HDHHI)</t>
+          <t>SCF Mitre</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -36943,14 +37315,14 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Puteri Santubong (ex-Hull 3295)' — hull-number former name written as the QC §2 placeholder 'Hull 3295 (HDHHI)'</t>
+          <t>IGU 2026 prints 'Kool Boreas (ex-SCF Mitre)'</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -36960,7 +37332,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Hull 3299 (HSHI)</t>
+          <t>SCF Barents</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -36970,19 +37342,19 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Puteri Mayang (ex-Hull 3299)' — hull-number former name written as the QC §2 placeholder 'Hull 3299 (HSHI)'</t>
+          <t>IGU 2026 prints 'Kool Firn (ex-SCF Barents)'</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -36992,7 +37364,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Hull H1793A (Hudong)</t>
+          <t>Hull 3221 (HDHHI)</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -37002,19 +37374,19 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Limail (ex-Hudong Hull 1793A)' — hull-number former name written as the QC §2 placeholder 'Hull H1793A (Hudong)'</t>
+          <t>IGU 2026 prints 'New Brave (ex-3221)' — hull-number former name written as the QC §2 placeholder 'Hull 3221 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>172</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -37024,7 +37396,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Hull 2527 (Hanwha)</t>
+          <t>Hull 3224 (HDHHI)</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -37039,14 +37411,14 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'MOL Azure (ex-Hull 2527)' — hull-number former name written as the QC §2 placeholder 'Hull 2527 (Hanwha)'</t>
+          <t>IGU 2026 prints 'New Green ST (ex-3224)' — hull-number former name written as the QC §2 placeholder 'Hull 3224 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -37056,7 +37428,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Hull 3225 (HDHHI)</t>
+          <t>Hull 3222 (HDHHI)</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -37071,14 +37443,14 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'New Oasis (ex-Hyundai 3225)' — hull-number former name written as the QC §2 placeholder 'Hull 3225 (HDHHI)'</t>
+          <t>IGU 2026 prints 'New Nature (ex-3222)' — hull-number former name written as the QC §2 placeholder 'Hull 3222 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -37088,7 +37460,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Hull 2566 (Hanwha)</t>
+          <t>Hull 2592 (SHI)</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -37103,14 +37475,14 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Esteem Fuji (ex-Hull 2566)' — hull-number former name written as the QC §2 placeholder 'Hull 2566 (Hanwha)'</t>
+          <t>IGU 2026 prints 'Orion Spirit (ex-2592)' — hull-number former name written as the QC §2 placeholder 'Hull 2592 (SHI)'</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -37120,7 +37492,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Hull 2537 (Hanwha)</t>
+          <t>Hull 2315 (SHI)</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -37130,19 +37502,19 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>PASS (corroborates)</t>
+          <t>PASS (OK (all tokens present))</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Maran Gas Syros (ex-ABCDE (2537))' — hull-number former name written as the QC §2 placeholder 'Hull 2537 (Hanwha)'</t>
+          <t>IGU 2026 prints 'Pacific Success (ex-Samsung Heavy Industries 2315)' — hull-number former name written as the QC §2 placeholder 'Hull 2315 (SHI)'</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>176</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -37152,7 +37524,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Hull H1892A (Hudong)</t>
+          <t>Hull 3297 (HDHHI)</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -37162,44 +37534,460 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (all tokens present))</t>
+          <t>PASS (corroborates)</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>IGU 2026 prints 'Ocean Inspiration (ex-Hudong-Zhonghua H1892A)' — hull-number former name written as the QC §2 placeholder 'Hull H1892A (Hudong)'</t>
+          <t>IGU 2026 prints 'Puteri Ledang (ex-Hull 3297)' — hull-number former name written as the QC §2 placeholder 'Hull 3297 (HDHHI)'</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Hull 3298 (HDHHI)</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'Puteri Mahsuri (ex-Hull 3298)' — hull-number former name written as the QC §2 placeholder 'Hull 3298 (HDHHI)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>Hull 3295 (HDHHI)</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'Puteri Santubong (ex-Hull 3295)' — hull-number former name written as the QC §2 placeholder 'Hull 3295 (HDHHI)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Hull 3299 (HSHI)</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'Puteri Mayang (ex-Hull 3299)' — hull-number former name written as the QC §2 placeholder 'Hull 3299 (HSHI)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Hull H1793A (Hudong)</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (all tokens present))</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'Limail (ex-Hudong Hull 1793A)' — hull-number former name written as the QC §2 placeholder 'Hull H1793A (Hudong)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Hull 2527 (Hanwha)</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'MOL Azure (ex-Hull 2527)' — hull-number former name written as the QC §2 placeholder 'Hull 2527 (Hanwha)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Hull 3225 (HDHHI)</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'New Oasis (ex-Hyundai 3225)' — hull-number former name written as the QC §2 placeholder 'Hull 3225 (HDHHI)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Hull 2566 (Hanwha)</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'Esteem Fuji (ex-Hull 2566)' — hull-number former name written as the QC §2 placeholder 'Hull 2566 (Hanwha)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Hull 2537 (Hanwha)</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'Maran Gas Syros (ex-ABCDE (2537))' — hull-number former name written as the QC §2 placeholder 'Hull 2537 (Hanwha)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Hull H1892A (Hudong)</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (all tokens present))</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>IGU 2026 prints 'Ocean Inspiration (ex-Hudong-Zhonghua H1892A)' — hull-number former name written as the QC §2 placeholder 'Hull H1892A (Hudong)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
           <t>1111</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>Other names</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
         <is>
           <t>Hull 2535 (Hanwha)</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>PASS (corroborates)</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>IGU 2026 prints 'Woodside Barrumbara (ex-2535)' — hull-number former name written as the QC §2 placeholder 'Hull 2535 (Hanwha)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Vivit City LNG</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Name stays 'Vivirt City LNG' (shipvault, marinetraffic.org, vesseltracker.com); IGU 2026 prints 'Vivit City LNG' — probably IGU's misspelling; reject to leave it out [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Ergy</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vesseltracker.com/en/Ships/Ergy-9250725.html</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>PASS (corroborates)</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Name stays IGU's 'Hongkong Energy' (the trading name); every database prints the demolition-voyage name 'Ergy' for IMO 9250725 (shipvault: SCRAPPED) — carried here. Status is still `active`: needs a scrapped fix [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Ergy</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/116466</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Name stays IGU's 'Hongkong Energy' (the trading name); every database prints the demolition-voyage name 'Ergy' for IMO 9250725 (shipvault: SCRAPPED) — carried here. Status is still `active`: needs a scrapped fix [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Other names</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Ergy</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/116466</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Name stays IGU's 'Hongkong Energy' (the trading name); every database prints the demolition-voyage name 'Ergy' for IMO 9250725 (shipvault: SCRAPPED) — carried here. Status is still `active`: needs a scrapped fix [IGU 2026 was the sole source; databases checked by IMO (Baird 2026-09-21)]</t>
         </is>
       </c>
     </row>
